--- a/forms/trg/Formulir_TRG_oralmicrobiome-rg.xlsx
+++ b/forms/trg/Formulir_TRG_oralmicrobiome-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B32)</f>
+        <f>COUNTA(Anggota!B5:B33)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F32)</f>
+        <f>COUNTA(Anggota!F5:F33)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,18 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof Dr drg Irene Riewpassa POB</t>
+          <t>Maria Tanumihardja</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
+          <t>endodontic microbiology &amp; herbal extraxts</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Drg Erni Marlina PhD, Sp.OM</t>
+          <t>Prof Dr drg Irene Riewpassa POB</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -979,12 +979,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof Dr drg M.Harun Achmad SpKGA (K)</t>
+          <t>Drg Erni Marlina PhD, Sp.OM</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof Dr drg SriOktawati Sp. Perio (K)</t>
+          <t>Prof Dr drg M.Harun Achmad SpKGA (K)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof drg Nurhayaty Natsir PhD Sp.KR (K)</t>
+          <t>Prof Dr drg SriOktawati Sp. Perio (K)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1078,18 +1078,18 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof Thantrira Porntaeethus</t>
+          <t>Prof drg Nurhayaty Natsir PhD Sp.KR (K)</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Nurul Ain</t>
+          <t>Prof Thantrira Porntaeethus</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1144,18 +1144,18 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>drg Rafikah D A.</t>
+          <t>Nurul Ain</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External Collaborator</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>drg Shinta L. T</t>
+          <t>drg Rafikah D A.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>drg Maria Flora</t>
+          <t>drg Shinta L. T</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>drg Resky Putri Amaliyah</t>
+          <t>drg Maria Flora</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1276,18 +1276,18 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Navila AK Rizal P</t>
+          <t>drg Resky Putri Amaliyah</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Student</t>
+          <t>Researchers</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Nasywa K.S.Aminuddin</t>
+          <t>Navila AK Rizal P</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>drg Beatrix Enoch</t>
+          <t>Nasywa K.S.Aminuddin</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>drg Juwita Purnamasari</t>
+          <t>drg Beatrix Enoch</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>drg Anjelia G. Bagiada</t>
+          <t>drg Juwita Purnamasari</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
@@ -1439,10 +1439,26 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>drg Anjelia G. Bagiada</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Doctoral Student</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>The oral cavity is a highly complex environment responsible for receiving and processing food, with teeth serving an essential function in these activities. These structures are continually subjected to mechanical wear and chemical challenges, with the oral microbiome playing an important role in these processes. In healthy conditions, the tooth’s most vulnerable tissues microenvironment that influences the pulp and root canal system remain sealed off, preventing contact with both pathogens and normally harmless resident bacteria</t>
+        </is>
+      </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
@@ -1450,7 +1466,11 @@
       <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1639,15 +1659,32 @@
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="12" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
